--- a/Result/profitability/3465.xlsx
+++ b/Result/profitability/3465.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02999999999999996</v>
+        <v>-0.03250000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>18.23125</v>
+        <v>17.68125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05375000000000003</v>
+        <v>-0.1475</v>
       </c>
       <c r="N3" t="n">
-        <v>18.03125</v>
+        <v>17.47125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.17875</v>
+        <v>-0.2425</v>
       </c>
       <c r="N4" t="n">
-        <v>17.52625</v>
+        <v>16.9575</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.43125</v>
+        <v>-0.27125</v>
       </c>
       <c r="N5" t="n">
-        <v>14.1425</v>
+        <v>13.265</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>-0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3325</v>
+        <v>-0.345</v>
       </c>
       <c r="N6" t="n">
-        <v>13.175</v>
+        <v>13.03</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.57</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6825</v>
       </c>
       <c r="N7" t="n">
-        <v>5.911250000000001</v>
+        <v>5.367500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6675</v>
+        <v>-0.5287500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>5.550000000000001</v>
+        <v>6.786249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>-0.79</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.65125</v>
+        <v>-0.6512500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.671250000000001</v>
+        <v>8.671249999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.585</v>
+        <v>-0.5850000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>9.6</v>
@@ -1772,7 +1772,7 @@
         <v>-0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6024999999999999</v>
+        <v>-0.6025</v>
       </c>
       <c r="N11" t="n">
         <v>10.25625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3465</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>617</v>
+      </c>
+      <c r="D75" t="n">
+        <v>519</v>
+      </c>
+      <c r="E75" t="n">
+        <v>98</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.11625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.81875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.206521739130435</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.670608108108108</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.174311926605505</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.019999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.307490144546649</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
